--- a/artfynd/A 69219-2020 artfynd.xlsx
+++ b/artfynd/A 69219-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129523844</v>
       </c>
       <c r="B2" t="n">
-        <v>58444</v>
+        <v>58447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 69219-2020 artfynd.xlsx
+++ b/artfynd/A 69219-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129523844</v>
       </c>
       <c r="B2" t="n">
-        <v>58447</v>
+        <v>58452</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 69219-2020 artfynd.xlsx
+++ b/artfynd/A 69219-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129523844</v>
       </c>
       <c r="B2" t="n">
-        <v>58452</v>
+        <v>58453</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
